--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegistDel.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\tamsDoubleBranch\tams-svreport-parent\tams-svreport\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2715" windowWidth="15210" windowHeight="3480"/>
+    <workbookView xWindow="0" yWindow="2712" windowWidth="15216" windowHeight="3480"/>
   </bookViews>
   <sheets>
     <sheet name="投资者身份信息-批量删除" sheetId="1" r:id="rId1"/>
@@ -15,12 +20,11 @@
     <definedName name="jgzjlb">填写说明!#REF!</definedName>
   </definedNames>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>版本号</t>
   </si>
@@ -120,6 +124,10 @@
     <t>3.必填要素前标“**”，选择性必填要素前标“*”，选填要素前无特殊标记；</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="19" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -128,7 +136,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="28" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -444,7 +452,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -563,6 +571,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -701,7 +724,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -735,6 +758,9 @@
     </xf>
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="45">
@@ -1127,22 +1153,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="7" customWidth="1"/>
+    <col min="3" max="3" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2"/>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1153,28 +1183,28 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:A4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.75" style="6" customWidth="1"/>
+    <col min="1" max="1" width="53.77734375" style="6" customWidth="1"/>
     <col min="2" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="54" customHeight="1">
+    <row r="1" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:1" ht="46.5" customHeight="1">
+    <row r="2" spans="1:1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="23.25" customHeight="1">
+    <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:1" ht="28.5">
+    <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
         <v>10</v>
       </c>
@@ -1189,12 +1219,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="52.875" customWidth="1"/>
+    <col min="2" max="2" width="52.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1202,7 +1232,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>1</v>
       </c>
@@ -1210,7 +1240,7 @@
         <v>43250</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="67.5">
+    <row r="3" spans="1:2" ht="69" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>

--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegistDel.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/EquityInfoRegistDel.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>版本号</t>
   </si>
@@ -124,10 +124,6 @@
     <t>3.必填要素前标“**”，选择性必填要素前标“*”，选填要素前无特殊标记；</t>
     <phoneticPr fontId="27" type="noConversion"/>
   </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="19" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -342,7 +338,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="19">
+  <fills count="20">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -451,26 +447,19 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -597,7 +586,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -612,7 +601,7 @@
     <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -627,28 +616,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -657,10 +646,10 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -732,15 +721,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="42" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="22" fillId="7" borderId="5" xfId="18" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="2" borderId="0" xfId="44" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -759,7 +743,10 @@
     <xf numFmtId="49" fontId="26" fillId="0" borderId="0" xfId="44" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="22" fillId="0" borderId="0" xfId="18" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="1" fillId="19" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1155,23 +1142,22 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" style="11" customWidth="1"/>
+    <col min="2" max="2" width="19.109375" style="12" customWidth="1"/>
     <col min="3" max="3" width="9.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="14" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
-        <v>11</v>
-      </c>
+    <row r="2" spans="1:2" s="13" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
     </row>
   </sheetData>
   <phoneticPr fontId="19" type="noConversion"/>
@@ -1185,27 +1171,27 @@
   <dimension ref="A1:A4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.77734375" style="6" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="53.77734375" style="4" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="10" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+      <c r="A4" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1225,18 +1211,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="8">
         <v>43250</v>
       </c>
     </row>
